--- a/results/log_pv_inst_fit/log_pv_inst_fit_densities_pdensity_estimates.xlsx
+++ b/results/log_pv_inst_fit/log_pv_inst_fit_densities_pdensity_estimates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,41 +462,11 @@
           <t>densities-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_inst_fit ~ (densities): pdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-inverse_distance-Running PooledOLS:inverse_distance for log_pv_inst_fit ~ (densities): pdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-k_nearest-Running PooledOLS:k_nearest for log_pv_inst_fit ~ (densities): pdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-queen-Running PooledOLS:queen for log_pv_inst_fit ~ (densities): pdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-inverse_distance-Running PanelRE:inverse_distance for log_pv_inst_fit ~ (densities): pdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-k_nearest-Running PanelRE:k_nearest for log_pv_inst_fit ~ (densities): pdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-queen-Running PanelRE:queen for log_pv_inst_fit ~ (densities): pdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pdensity</t>
+          <t>D(Population)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,43 +512,13 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>0.008***</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-0.006***</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-0.006***</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-0.006***</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-0.007***</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>-0.007***</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>-0.007***</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -624,43 +564,13 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>0.125+</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-0.848***</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-0.848***</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-0.848***</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2.023***</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2.023***</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2.023***</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -706,43 +616,13 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>0.003*</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.035***</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.035***</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.035***</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -788,126 +668,96 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>0.191***</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.703***</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.703***</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.703***</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-0.174***</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-0.174***</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.174***</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W_pdensity</t>
+          <t>Spatial term, ρ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.873***</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.707***</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.004*</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>0.606***</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.963***</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.788***</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.698***</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W_log_income</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.491**</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.742***</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.958***</t>
-        </is>
-      </c>
+          <t>Spatial term, λ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.973***</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.894***</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.848***</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_log_hholds</t>
+          <t>W(D(Population))</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.061***</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.008*</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.008***</t>
+          <t>-0.004*</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -916,32 +766,26 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W_log_sunny_hours</t>
+          <t>W(Income)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.270***</t>
+          <t>0.491**</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.321***</t>
+          <t>0.742***</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.315***</t>
+          <t>0.958***</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -950,891 +794,320 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W_log_pv_inst_fit</t>
+          <t>W(Households)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.873***</t>
+          <t>-0.061***</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.707***</t>
+          <t>-0.008*</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.606***</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.963***</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.788***</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.698***</t>
-        </is>
-      </c>
+          <t>-0.008***</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>W(Sunny hours)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>-0.270***</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.831</t>
+          <t>-0.321***</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.817</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.852</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.827</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.809</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.036</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.187</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.299</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.259</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.259</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.259</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
+          <t>-0.315***</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aic</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-9843.531</t>
+          <t>0.853</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-9416.114</t>
+          <t>0.831</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-9217.148</t>
+          <t>0.817</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-9811.052</t>
+          <t>0.852</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9314.066</t>
+          <t>0.827</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9055.386</t>
+          <t>0.809</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9827.049</t>
+          <t>0.036</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-9224.577</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8872.616</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1112.555</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1112.555</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1112.555</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2306.310</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2306.310</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2306.310</t>
+          <t>0.299</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>schwarz</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-9792.787</t>
+          <t>-9843.531</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-9365.370</t>
+          <t>-9416.114</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-9166.404</t>
+          <t>-9217.148</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-9782.861</t>
+          <t>-9811.052</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-9285.875</t>
+          <t>-9314.066</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9027.195</t>
+          <t>-9055.386</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-9804.496</t>
+          <t>-9827.049</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-9202.024</t>
+          <t>-9224.577</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-8850.063</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>1140.746</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1140.746</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>1140.746</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2334.501</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2334.501</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2334.501</t>
+          <t>-8872.616</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>llr</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4930.765</t>
+          <t>-9792.787</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4717.057</t>
+          <t>-9365.370</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4617.574</t>
+          <t>-9166.404</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4910.526</t>
+          <t>-9782.861</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4662.033</t>
+          <t>-9285.875</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4532.693</t>
+          <t>-9027.195</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4917.524</t>
+          <t>-9804.496</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4616.288</t>
+          <t>-9202.024</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4440.308</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>-551.277</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-551.277</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>-551.277</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-1148.155</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-1148.155</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-1148.155</t>
+          <t>-8850.063</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>Log-Likelihood</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4930.765</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4717.057</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4617.574</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4910.526</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4662.033</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4532.693</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4917.524</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4616.288</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2076</t>
+          <t>4440.308</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    67.230287   1      0.0
-1  LM Marginal Spatial (LM2)    17.683298   1      0.0
-2             LM Joint (LMJ)  4832.610534   2      0.0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df       p-value
-0       LM Marginal RE (LM1)    67.230287   1  0.000000e+00
-1  LM Marginal Spatial (LM2)     8.159576   1  2.220446e-16
-2             LM Joint (LMJ)  4586.490205   2  0.000000e+00</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df       p-value
-0       LM Marginal RE (LM1)    67.230287   1  0.000000e+00
-1  LM Marginal Spatial (LM2)     7.457593   1  4.407585e-14
-2             LM Joint (LMJ)  4575.527219   2  0.000000e+00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial  152.876787  1     0.0
-1  Hausman Specification Test  -79.822123  4     1.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df p-value
-0      LM Conditional Spatial  38.125975  1     0.0
-1  Hausman Specification Test -79.822123  4     1.0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df p-value
-0      LM Conditional Spatial  25.252381  1     0.0
-1  Hausman Specification Test -79.822123  4     1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           pdensity     0.007852  0.001103   7.117399       0.0
-1         log_income    -0.178366  0.074461  -2.395428  0.016601
-2         log_hholds     0.001085  0.001179   0.920449  0.357338
-3    log_sunny_hours     0.169739  0.034122   4.974553  0.000001
-4         W_pdensity     0.013836  0.013867   0.997808  0.318372
-5       W_log_income     0.491168  0.159204   3.085155  0.002034
-6       W_log_hholds    -0.061245    0.0168  -3.645635  0.000267
-7  W_log_sunny_hours    -0.270364  0.054444  -4.965942  0.000001
-8  W_log_pv_inst_fit     0.873307  0.029888  29.219325       0.0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           pdensity     0.007721  0.001188   6.500718       0.0
-1         log_income    -0.095832  0.076133  -1.258753  0.208119
-2         log_hholds     0.001259  0.001268   0.992775   0.32082
-3    log_sunny_hours     0.153842  0.034728   4.429897  0.000009
-4         W_pdensity     0.000837  0.004084   0.204953  0.837609
-5       W_log_income     0.741947   0.09717   7.635562       0.0
-6       W_log_hholds    -0.007926  0.003783  -2.095373  0.036138
-7  W_log_sunny_hours    -0.321287  0.045881  -7.002639       0.0
-8  W_log_pv_inst_fit      0.70715  0.020846  33.922342       0.0</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           pdensity     0.008274  0.001245   6.645851       0.0
-1         log_income    -0.062608  0.075887  -0.825014  0.409363
-2         log_hholds     0.001466  0.001319   1.111723  0.266257
-3    log_sunny_hours     0.119787  0.035345   3.389112  0.000701
-4         W_pdensity    -0.003881  0.001829  -2.121752  0.033859
-5       W_log_income     0.957501  0.085367  11.216282       0.0
-6       W_log_hholds    -0.008123  0.002164  -3.753248  0.000175
-7  W_log_sunny_hours    -0.314612  0.043975  -7.154349       0.0
-8  W_log_pv_inst_fit      0.60618   0.02107  28.769228       0.0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err     zt_stat      prob
-0           pdensity     0.007673  0.001104    6.948726       0.0
-1         log_income    -0.038866  0.026562    -1.46324  0.143402
-2         log_hholds     0.001349  0.001183    1.140469  0.254091
-3    log_sunny_hours     0.078669  0.025172    3.125195  0.001777
-4  W_log_pv_inst_fit     0.963435  0.009315  103.428701       0.0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           pdensity     0.007243  0.001196   6.054871       0.0
-1         log_income     0.339895  0.038364   8.859639       0.0
-2         log_hholds     0.001923  0.001281   1.500751   0.13342
-3    log_sunny_hours     0.032842  0.025197   1.303402  0.192438
-4  W_log_pv_inst_fit     0.787649  0.015699  50.172806       0.0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           pdensity     0.008523  0.001258    6.77571       0.0
-1         log_income     0.515286  0.042142  12.227295       0.0
-2         log_hholds     0.002103  0.001347   1.560584  0.118622
-3    log_sunny_hours     0.015203  0.026424   0.575337  0.565064
-4  W_log_pv_inst_fit     0.698468  0.016991  41.108763       0.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err     zt_stat      prob
-0         pdensity     0.007851  0.001101     7.13239       0.0
-1       log_income    -0.160335  0.074237   -2.159762  0.030791
-2       log_hholds     0.001447  0.001176    1.230219  0.218615
-3  log_sunny_hours     0.171003  0.034159    5.006042  0.000001
-4           lambda     0.972966  0.007543  128.995405       0.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         pdensity     0.007114  0.001137   6.257797       0.0
-1       log_income     0.051192  0.073057   0.700714  0.483481
-2       log_hholds     0.002343  0.001208   1.938866  0.052518
-3  log_sunny_hours     0.192935   0.03496   5.518668       0.0
-4           lambda     0.894015  0.009818  91.061548       0.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         pdensity     0.007918  0.001029   7.695151       0.0
-1       log_income     0.125444  0.071961   1.743232  0.081293
-2       log_hholds     0.003035  0.001183   2.564222  0.010341
-3  log_sunny_hours     0.191114  0.035967   5.313597       0.0
-4           lambda     0.847852  0.011953  70.932379       0.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     4.469566  0.498409   8.967665       0.0
-1         pdensity    -0.006152  0.000304 -20.202949       0.0
-2       log_income    -0.847818  0.074435 -11.390061       0.0
-3       log_hholds     0.034587    0.0085   4.068831  0.000049
-4  log_sunny_hours     0.703173  0.151807   4.632036  0.000004</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     4.469566  0.498409   8.967665       0.0
-1         pdensity    -0.006152  0.000304 -20.202949       0.0
-2       log_income    -0.847818  0.074435 -11.390061       0.0
-3       log_hholds     0.034587    0.0085   4.068831  0.000049
-4  log_sunny_hours     0.703173  0.151807   4.632036  0.000004</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     4.469566  0.498409   8.967665       0.0
-1         pdensity    -0.006152  0.000304 -20.202949       0.0
-2       log_income    -0.847818  0.074435 -11.390061       0.0
-3       log_hholds     0.034587    0.0085   4.068831  0.000049
-4  log_sunny_hours     0.703173  0.151807   4.632036  0.000004</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     -4.84678  0.203824 -23.779233       0.0
-1         pdensity    -0.007236  0.000701 -10.322092       0.0
-2       log_income     2.022705  0.043186  46.836774       0.0
-3       log_hholds     0.000267  0.002213   0.120593  0.904013
-4  log_sunny_hours    -0.174237  0.043261  -4.027543  0.000056</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     -4.84678  0.203824 -23.779233       0.0
-1         pdensity    -0.007236  0.000701 -10.322092       0.0
-2       log_income     2.022705  0.043186  46.836774       0.0
-3       log_hholds     0.000267  0.002213   0.120593  0.904013
-4  log_sunny_hours    -0.174237  0.043261  -4.027543  0.000056</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     -4.84678  0.203824 -23.779233       0.0
-1         pdensity    -0.007236  0.000701 -10.322092       0.0
-2       log_income     2.022705  0.043186  46.836774       0.0
-3       log_hholds     0.000267  0.002213   0.120593  0.904013
-4  log_sunny_hours    -0.174237  0.043261  -4.027543  0.000056</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_inverse_distance  \
-pdensity                                     0.171192   
-log_income                                   2.468977   
-log_hholds                                  -0.474848   
-log_sunny_hours                             -0.794240   
-                 direct_ML_LagFE(SLX)_inverse_distance  \
-pdensity                                      0.007852   
-log_income                                   -0.178366   
-log_hholds                                    0.001085   
-log_sunny_hours                               0.169739   
-                 indirect_ML_LagFE(SLX)_inverse_distance  
-pdensity                                        0.163340  
-log_income                                      2.647344  
-log_hholds                                     -0.475934  
-log_sunny_hours                                -0.963980  </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_k_nearest  \
-pdensity                              0.029224   
-log_income                            2.206296   
-log_hholds                           -0.022766   
-log_sunny_hours                      -0.571776   
-                 direct_ML_LagFE(SLX)_k_nearest  \
-pdensity                               0.007721   
-log_income                            -0.095832   
-log_hholds                             0.001259   
-log_sunny_hours                        0.153842   
-                 indirect_ML_LagFE(SLX)_k_nearest  
-pdensity                                 0.021503  
-log_income                               2.302128  
-log_hholds                              -0.024025  
-log_sunny_hours                         -0.725618  </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
-pdensity                          0.011156                    0.008274   
-log_income                        2.272343                   -0.062608   
-log_hholds                       -0.016904                    0.001466   
-log_sunny_hours                  -0.494706                    0.119787   
-                 indirect_ML_LagFE(SLX)_queen  
-pdensity                             0.002882  
-log_income                           2.334951  
-log_hholds                          -0.018370  
-log_sunny_hours                     -0.614494  </t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_inverse_distance  \
-pdensity                                0.209854   
-log_income                             -1.062936   
-log_hholds                              0.036903   
-log_sunny_hours                         2.151482   
-                 direct_ML_LagFE_inverse_distance  \
-pdensity                                 0.007673   
-log_income                              -0.038866   
-log_hholds                               0.001349   
-log_sunny_hours                          0.078669   
-                 indirect_ML_LagFE_inverse_distance  
-pdensity                                   0.202181  
-log_income                                -1.024069  
-log_hholds                                 0.035553  
-log_sunny_hours                            2.072813  </t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
-pdensity                         0.034109                   0.007243   
-log_income                       1.600630                   0.339895   
-log_hholds                       0.009055                   0.001923   
-log_sunny_hours                  0.154659                   0.032842   
-                 indirect_ML_LagFE_k_nearest  
-pdensity                            0.026866  
-log_income                          1.260735  
-log_hholds                          0.007132  
-log_sunny_hours                     0.121817  </t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_queen  direct_ML_LagFE_queen  \
-pdensity                     0.028266               0.008523   
-log_income                   1.708894               0.515286   
-log_hholds                   0.006973               0.002103   
-log_sunny_hours              0.050418               0.015203   
-                 indirect_ML_LagFE_queen  
-pdensity                        0.019743  
-log_income                      1.193608  
-log_hholds                      0.004870  
-log_sunny_hours                 0.035215  </t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>lambda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.973***</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.894***</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.848***</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CONSTANT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>4.470***</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>4.470***</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>4.470***</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-4.847***</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-4.847***</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>-4.847***</t>
+          <t>N obs.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2076</t>
         </is>
       </c>
     </row>
